--- a/Demo/ONCHO/epi/demo_oncho_epi_9999_2_part.xlsx
+++ b/Demo/ONCHO/epi/demo_oncho_epi_9999_2_part.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yumbad\Repositories\dsa-forms\Demo\ONCHO\epi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E98F2FE8-BA48-4018-828A-5D450BB57E75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{158F4C55-0D21-48EA-9EDB-14F8ACDFAEC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
